--- a/public/downloads/公开名单-CPI-离岸-FATF_20261024.xlsx
+++ b/public/downloads/公开名单-CPI-离岸-FATF_20261024.xlsx
@@ -98,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -120,6 +120,9 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5059,10 +5062,10 @@
     <col width="44" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>来源: FATF — High-Risk Jurisdictions subject to a Call for Action(黑) / Jurisdictions under Increased Monitoring(灰) · 与本次官方抓取一致（同一期 2026-06），采用法务确认口径，名单日期 2026-06-19（法务维护的基线） · 抓取尝试: 2026-10-24</t>
+    <row r="1" ht="54" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>⚠ 本次抓取失败，使用法务基线（非本次抓取） · 名单日期: 2026-06-19（法务维护的基线） · 抓取尝试: 2026-10-24 · 来源: FATF — High-Risk Jurisdictions subject to a Call for Action(黑) / Jurisdictions under Increased Monitoring(灰)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
